--- a/data/onedrive/Comunidades_Energeticas_Avance.xlsx
+++ b/data/onedrive/Comunidades_Energeticas_Avance.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -3915,14 +3915,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="8f154a8c-a0d7-469f-a565-81a8dee811c9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006A9EC2A4CBCD7C4D95E7C32E44BE2AFE" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0395f90c593ea1a580452366e8ba0320">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8f154a8c-a0d7-469f-a565-81a8dee811c9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4f0abcea501e1de3eee851a4c8298e86" ns3:_="">
     <xsd:import namespace="8f154a8c-a0d7-469f-a565-81a8dee811c9"/>
@@ -4110,14 +4102,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8f154a8c-a0d7-469f-a565-81a8dee811c9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0787518D-69BD-4E45-AC35-D1E5AC391598}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51E095F6-BF66-41A9-AB03-40D964033B2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A89F9449-5121-46A4-8510-26BE340E38AC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A89F9449-5121-46A4-8510-26BE340E38AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51E095F6-BF66-41A9-AB03-40D964033B2A}"/>
 </file>
--- a/data/onedrive/Comunidades_Energeticas_Avance.xlsx
+++ b/data/onedrive/Comunidades_Energeticas_Avance.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -3906,12 +3906,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8f154a8c-a0d7-469f-a565-81a8dee811c9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4103,15 +4102,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="8f154a8c-a0d7-469f-a565-81a8dee811c9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0787518D-69BD-4E45-AC35-D1E5AC391598}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51E095F6-BF66-41A9-AB03-40D964033B2A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4119,5 +4119,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51E095F6-BF66-41A9-AB03-40D964033B2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0787518D-69BD-4E45-AC35-D1E5AC391598}"/>
 </file>